--- a/public/templates/termo_colaboracao.xlsx
+++ b/public/templates/termo_colaboracao.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orientacoes" sheetId="1" r:id="R1f1fc7c44c434d3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ajuste" sheetId="2" r:id="R57d309fe91a047a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contratos" sheetId="3" r:id="Redc90746274c4c9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Naturezas_Contrato" sheetId="4" r:id="R22600b34bff74344"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documentos_Fiscais" sheetId="5" r:id="R5e918f81de434c37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pagamentos" sheetId="6" r:id="R4a5bf03e035a45c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funcionarios" sheetId="7" r:id="R3bb40e07e05e4411"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Salarios" sheetId="8" r:id="R7631880ce6914783"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remuneracoes_Func" sheetId="9" r:id="R69e16a507eba4e83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dicionario" sheetId="10" r:id="R24560f3feb9b46d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orientacoes" sheetId="1" r:id="Rff3eae3c0068477d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ajuste" sheetId="2" r:id="Rb0fd621d2b614617"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contratos" sheetId="3" r:id="R70eee062dc2740fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Naturezas_Contrato" sheetId="4" r:id="R5ee41b94d7aa40b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documentos_Fiscais" sheetId="5" r:id="R1648e3c0027847ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pagamentos" sheetId="6" r:id="Rbd4ca57c69224571"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funcionarios" sheetId="7" r:id="R6b622bc4b1ce4de1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Salarios" sheetId="8" r:id="R90a13e2b96e14102"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remuneracoes_Func" sheetId="9" r:id="R41600cc432554799"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dicionario" sheetId="10" r:id="Ra4853151dec646b3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -391,10 +391,10 @@
     </x:row>
     <x:row r="10" ht="26" customHeight="1">
       <x:c r="A10" s="1" t="str">
-        <x:v>CSV alternativo</x:v>
+        <x:v>Arquivo de carga</x:v>
       </x:c>
       <x:c r="B10" s="1" t="str">
-        <x:v>Um CSV UTF-8 por aba. Use o nome da aba como nome do arquivo. Ajuste.csv é obrigatório.</x:v>
+        <x:v>Envie somente um arquivo XLSX com todas as abas do ajuste.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
